--- a/Docs/Tabela_z_nazwami_kolumn_i_komentarzami.xlsx
+++ b/Docs/Tabela_z_nazwami_kolumn_i_komentarzami.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kacpe\OneDrive\Pulpit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Studia\IPZ-Pewniaczki\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE3875CF-07BC-4594-BDAC-2B5AF2F5CD00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329D992A-9261-47C9-ABBD-B6290A415F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5748" yWindow="360" windowWidth="17280" windowHeight="8880" xr2:uid="{AA918570-661E-45F6-89F6-738A95499EEA}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{AA918570-661E-45F6-89F6-738A95499EEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="119">
   <si>
     <t>Nazwa Kolumny</t>
   </si>
@@ -427,6 +427,54 @@
   </si>
   <si>
     <t>Wzór matematyczny</t>
+  </si>
+  <si>
+    <t>FTHG</t>
+  </si>
+  <si>
+    <t>Ilość zdobytych goli na koniec meczu przez gospodarzy</t>
+  </si>
+  <si>
+    <t>FTAG</t>
+  </si>
+  <si>
+    <t>Ilość zdobytych goli na koniec meczu przez gości</t>
+  </si>
+  <si>
+    <t>HomeMatchday</t>
+  </si>
+  <si>
+    <t>Numer kolejki gospodarzy</t>
+  </si>
+  <si>
+    <t>AwayMatchday</t>
+  </si>
+  <si>
+    <t>Numer kolejki gości</t>
+  </si>
+  <si>
+    <t>isSuprise_H</t>
+  </si>
+  <si>
+    <t>Czy mecz zakończył się niespodzianką gospodarzy</t>
+  </si>
+  <si>
+    <t>Czy mecz zakończył się niespodzianką gości</t>
+  </si>
+  <si>
+    <t>Czy mecz zakończył się niespodzianką remis</t>
+  </si>
+  <si>
+    <t>isSuprise_D</t>
+  </si>
+  <si>
+    <t>isSuprise_A</t>
+  </si>
+  <si>
+    <t>isSuprise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czy mecz zakończył się jaką kolwiek niespodzianką </t>
   </si>
 </sst>
 </file>
@@ -513,29 +561,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -965,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA06EDAE-231A-4D42-AFF7-DB4624B8F69F}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
@@ -975,661 +1023,719 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="1" t="e" vm="1">
+      <c r="D28" s="1"/>
+      <c r="E28" s="3" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="1" t="e" vm="2">
+      <c r="D29" s="1"/>
+      <c r="E29" s="3" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="1" t="e" vm="3">
+      <c r="D32" s="1"/>
+      <c r="E32" s="3" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="1" t="e" vm="4">
+      <c r="D35" s="1"/>
+      <c r="E35" s="3" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="1" t="e" vm="5">
+      <c r="D38" s="1"/>
+      <c r="E38" s="3" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D41" s="5"/>
-      <c r="E41" s="1" t="e" vm="6">
+      <c r="D41" s="1"/>
+      <c r="E41" s="3" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="5"/>
-      <c r="E44" s="1" t="e" vm="7">
+      <c r="D44" s="1"/>
+      <c r="E44" s="3" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="C7:C24"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="E38:G40"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="E41:G43"/>
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="E44:G46"/>
     <mergeCell ref="C29:C31"/>
@@ -1638,12 +1744,35 @@
     <mergeCell ref="E29:G31"/>
     <mergeCell ref="E32:G34"/>
     <mergeCell ref="E35:G37"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="C7:C24"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="E38:G40"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="E41:G43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="06e0fab9-d3c7-4228-8951-a381beafabee" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100898C99BFA6707C449FB5DEFD6C6B88D2" ma:contentTypeVersion="13" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="4233cc6462d02d07e0ae1fe028f05d54">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="06e0fab9-d3c7-4228-8951-a381beafabee" xmlns:ns4="4d8e724f-ed6c-4b7c-86a4-236d8fc22848" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bc2c63a7dad31bfee6583dfabf5fe5b2" ns3:_="" ns4:_="">
     <xsd:import namespace="06e0fab9-d3c7-4228-8951-a381beafabee"/>
@@ -1864,24 +1993,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{095922AC-C00C-4C3C-BB2B-E0AD90BB0401}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="06e0fab9-d3c7-4228-8951-a381beafabee"/>
+    <ds:schemaRef ds:uri="4d8e724f-ed6c-4b7c-86a4-236d8fc22848"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="06e0fab9-d3c7-4228-8951-a381beafabee" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FCC0122-E133-43C9-9977-532E7FF3F527}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A417F2B-CE74-45A8-BAE5-74E6674E54B9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1898,29 +2035,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FCC0122-E133-43C9-9977-532E7FF3F527}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{095922AC-C00C-4C3C-BB2B-E0AD90BB0401}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="06e0fab9-d3c7-4228-8951-a381beafabee"/>
-    <ds:schemaRef ds:uri="4d8e724f-ed6c-4b7c-86a4-236d8fc22848"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Docs/Tabela_z_nazwami_kolumn_i_komentarzami.xlsx
+++ b/Docs/Tabela_z_nazwami_kolumn_i_komentarzami.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Studia\IPZ-Pewniaczki\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329D992A-9261-47C9-ABBD-B6290A415F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083E48F1-4F52-4728-8FE7-CF5E3D8DE0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{AA918570-661E-45F6-89F6-738A95499EEA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA918570-661E-45F6-89F6-738A95499EEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="192">
   <si>
     <t>Nazwa Kolumny</t>
   </si>
@@ -138,9 +138,6 @@
     <t>nd.</t>
   </si>
   <si>
-    <t>Data</t>
-  </si>
-  <si>
     <t>Data rozegrania meczu</t>
   </si>
   <si>
@@ -475,52 +472,237 @@
   </si>
   <si>
     <t xml:space="preserve">Czy mecz zakończył się jaką kolwiek niespodzianką </t>
+  </si>
+  <si>
+    <t>HomeTeamPlacment</t>
+  </si>
+  <si>
+    <t>Pozycja gospodarzy w tabeli ligowej</t>
+  </si>
+  <si>
+    <t>AwayTeamPlacment</t>
+  </si>
+  <si>
+    <t>Pozycja gości w tabeli ligowej</t>
+  </si>
+  <si>
+    <t>HomeForm3</t>
+  </si>
+  <si>
+    <t>HomeForm5</t>
+  </si>
+  <si>
+    <t>HomeFormSeason</t>
+  </si>
+  <si>
+    <t>AwayForm3</t>
+  </si>
+  <si>
+    <t>AwayForm5</t>
+  </si>
+  <si>
+    <t>AwayFormSeason</t>
+  </si>
+  <si>
+    <t>HomeGoals3</t>
+  </si>
+  <si>
+    <t>HomeGoals5</t>
+  </si>
+  <si>
+    <t>HomeGoalsSeason</t>
+  </si>
+  <si>
+    <t>AwayGoals3</t>
+  </si>
+  <si>
+    <t>AwayGoals5</t>
+  </si>
+  <si>
+    <t>AwayGoalsSeason</t>
+  </si>
+  <si>
+    <t>Forma gospodarzy w 3 ostatnich meczach</t>
+  </si>
+  <si>
+    <t>Forma gospodarzy w 5 ostatnich meczach</t>
+  </si>
+  <si>
+    <t>Forma gospodarzy w sezonie</t>
+  </si>
+  <si>
+    <t>Forma gości w sezonie</t>
+  </si>
+  <si>
+    <t>Forma gości w 3 ostatnich meczach</t>
+  </si>
+  <si>
+    <t>Gole zdobyte gospodarzy w 3 ostatnich meczach</t>
+  </si>
+  <si>
+    <t>Gole zdobyte przez gości w sezonie</t>
+  </si>
+  <si>
+    <t>Gole zdobyte przez gospodarzy w sezonie</t>
+  </si>
+  <si>
+    <t>Gole zdobyte gości w 3 ostatnich meczach</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>BFH</t>
+  </si>
+  <si>
+    <t>BFD</t>
+  </si>
+  <si>
+    <t>BFA</t>
+  </si>
+  <si>
+    <t>BSH</t>
+  </si>
+  <si>
+    <t>BSD</t>
+  </si>
+  <si>
+    <t>BSA</t>
+  </si>
+  <si>
+    <t>GBH</t>
+  </si>
+  <si>
+    <t>GBD</t>
+  </si>
+  <si>
+    <t>GBA</t>
+  </si>
+  <si>
+    <t>PSH</t>
+  </si>
+  <si>
+    <t>PSD</t>
+  </si>
+  <si>
+    <t>PSA</t>
+  </si>
+  <si>
+    <t>SOH</t>
+  </si>
+  <si>
+    <t>SOD</t>
+  </si>
+  <si>
+    <t>SOA</t>
+  </si>
+  <si>
+    <t>SBH</t>
+  </si>
+  <si>
+    <t>SBD</t>
+  </si>
+  <si>
+    <t>SBA</t>
+  </si>
+  <si>
+    <t>SJH</t>
+  </si>
+  <si>
+    <t>SJD</t>
+  </si>
+  <si>
+    <t>SJA</t>
+  </si>
+  <si>
+    <t>SYH</t>
+  </si>
+  <si>
+    <t>SYD</t>
+  </si>
+  <si>
+    <t>SYA</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gospodarza w Betfair</t>
+  </si>
+  <si>
+    <t>Kurs na remis w Betfair</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gości w Betfair</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gospodarza w Blue Square</t>
+  </si>
+  <si>
+    <t>Kurs na remis w Blue Square</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gości w Blue Square</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gospodarza w Gamebookers</t>
+  </si>
+  <si>
+    <t>Kurs na remis w Gamebookers</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gości w Gamebookers</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gospodarza w Pinnacle</t>
+  </si>
+  <si>
+    <t>Kurs na remis w Pinnacle</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gości w Pinnacle</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gospodarza w Sporting Odds</t>
+  </si>
+  <si>
+    <t>Kurs na remis w Sporting Odds</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gości w Sporting Odds</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gospodarza w Sportingbet</t>
+  </si>
+  <si>
+    <t>Kurs na remis w Sportingbet</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gości w Sportingbet</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gospodarza w Stan James</t>
+  </si>
+  <si>
+    <t>Kurs na remis w Stan James</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gości w Stan James</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gospodarza w Stanleybet</t>
+  </si>
+  <si>
+    <t>Kurs na remis w Stanleybet</t>
+  </si>
+  <si>
+    <t>Kurs na wygraną gości w Stanleybet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -532,7 +714,48 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -558,20 +781,17 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -579,11 +799,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="45"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1013,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA06EDAE-231A-4D42-AFF7-DB4624B8F69F}">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
@@ -1023,719 +1246,1262 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="5" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="5" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="5" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="5" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="5" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="5" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="5" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="8"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" s="8"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="3" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="3" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="3" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="3" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="3" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" s="1"/>
-      <c r="E41" s="3" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="7" t="s">
+      <c r="B47" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C69" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="3" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>118</v>
-      </c>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C70" s="9"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C71" s="9"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C72" s="9"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C73" s="9"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C74" s="9"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C75" s="9"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C76" s="9"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C77" s="9"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C78" s="9"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C79" s="9"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" s="9"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C84" s="9"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C85" s="9"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C86" s="9"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C87" s="9"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" s="9"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C89" s="9"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C90" s="9"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C91" s="9"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C92" s="9"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="C69:C92"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="C7:C24"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="E38:G40"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="E41:G43"/>
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="E44:G46"/>
     <mergeCell ref="C29:C31"/>
@@ -1744,35 +2510,13 @@
     <mergeCell ref="E29:G31"/>
     <mergeCell ref="E32:G34"/>
     <mergeCell ref="E35:G37"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="C7:C24"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="E38:G40"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="E41:G43"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="06e0fab9-d3c7-4228-8951-a381beafabee" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100898C99BFA6707C449FB5DEFD6C6B88D2" ma:contentTypeVersion="13" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="4233cc6462d02d07e0ae1fe028f05d54">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="06e0fab9-d3c7-4228-8951-a381beafabee" xmlns:ns4="4d8e724f-ed6c-4b7c-86a4-236d8fc22848" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bc2c63a7dad31bfee6583dfabf5fe5b2" ns3:_="" ns4:_="">
     <xsd:import namespace="06e0fab9-d3c7-4228-8951-a381beafabee"/>
@@ -1993,32 +2737,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{095922AC-C00C-4C3C-BB2B-E0AD90BB0401}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="06e0fab9-d3c7-4228-8951-a381beafabee"/>
-    <ds:schemaRef ds:uri="4d8e724f-ed6c-4b7c-86a4-236d8fc22848"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FCC0122-E133-43C9-9977-532E7FF3F527}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="06e0fab9-d3c7-4228-8951-a381beafabee" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A417F2B-CE74-45A8-BAE5-74E6674E54B9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2035,4 +2771,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FCC0122-E133-43C9-9977-532E7FF3F527}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{095922AC-C00C-4C3C-BB2B-E0AD90BB0401}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="06e0fab9-d3c7-4228-8951-a381beafabee"/>
+    <ds:schemaRef ds:uri="4d8e724f-ed6c-4b7c-86a4-236d8fc22848"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Docs/Tabela_z_nazwami_kolumn_i_komentarzami.xlsx
+++ b/Docs/Tabela_z_nazwami_kolumn_i_komentarzami.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Studia\IPZ-Pewniaczki\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083E48F1-4F52-4728-8FE7-CF5E3D8DE0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D3F6EF-5382-4A6D-A009-53D480EFCE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA918570-661E-45F6-89F6-738A95499EEA}"/>
   </bookViews>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="196">
   <si>
     <t>Nazwa Kolumny</t>
   </si>
@@ -694,6 +694,18 @@
   </si>
   <si>
     <t>Kurs na wygraną gości w Stanleybet</t>
+  </si>
+  <si>
+    <t>HTLP</t>
+  </si>
+  <si>
+    <t>ATLP</t>
+  </si>
+  <si>
+    <t>Pozycja gospodarzy w tabeli ligowej w poprzednim sezonie</t>
+  </si>
+  <si>
+    <t>Pozycja gości w tabeli ligowej w poprzednim sezonie</t>
   </si>
 </sst>
 </file>
@@ -781,9 +793,6 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -791,12 +800,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+      <alignment vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -805,8 +817,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="45"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1236,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA06EDAE-231A-4D42-AFF7-DB4624B8F69F}">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
@@ -1246,1252 +1258,1268 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="5" t="e" vm="1">
+      <c r="D28" s="1"/>
+      <c r="E28" s="4" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="5" t="e" vm="2">
+      <c r="D29" s="1"/>
+      <c r="E29" s="4" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="5" t="e" vm="3">
+      <c r="D32" s="1"/>
+      <c r="E32" s="4" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="5" t="e" vm="4">
+      <c r="D35" s="1"/>
+      <c r="E35" s="4" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="5" t="e" vm="5">
+      <c r="D38" s="1"/>
+      <c r="E38" s="4" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="5" t="e" vm="6">
+      <c r="D41" s="1"/>
+      <c r="E41" s="4" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C42" s="7"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C43" s="7"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D44" s="2"/>
-      <c r="E44" s="5" t="e" vm="7">
+      <c r="D44" s="1"/>
+      <c r="E44" s="4" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C45" s="8"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C46" s="8"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C69" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C70" s="9"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C71" s="9"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C72" s="9"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C74" s="9"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C76" s="9"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C78" s="9"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C80" s="9"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C82" s="9"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C83" s="9"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C84" s="9"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C85" s="9"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C86" s="9"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C87" s="9"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
+      <c r="A88" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C88" s="9"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C89" s="9"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C90" s="9"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C91" s="9"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C92" s="9"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>195</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2517,6 +2545,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="06e0fab9-d3c7-4228-8951-a381beafabee" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100898C99BFA6707C449FB5DEFD6C6B88D2" ma:contentTypeVersion="13" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="4233cc6462d02d07e0ae1fe028f05d54">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="06e0fab9-d3c7-4228-8951-a381beafabee" xmlns:ns4="4d8e724f-ed6c-4b7c-86a4-236d8fc22848" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bc2c63a7dad31bfee6583dfabf5fe5b2" ns3:_="" ns4:_="">
     <xsd:import namespace="06e0fab9-d3c7-4228-8951-a381beafabee"/>
@@ -2737,24 +2782,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{095922AC-C00C-4C3C-BB2B-E0AD90BB0401}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="06e0fab9-d3c7-4228-8951-a381beafabee"/>
+    <ds:schemaRef ds:uri="4d8e724f-ed6c-4b7c-86a4-236d8fc22848"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="06e0fab9-d3c7-4228-8951-a381beafabee" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FCC0122-E133-43C9-9977-532E7FF3F527}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A417F2B-CE74-45A8-BAE5-74E6674E54B9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2771,29 +2824,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FCC0122-E133-43C9-9977-532E7FF3F527}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{095922AC-C00C-4C3C-BB2B-E0AD90BB0401}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="06e0fab9-d3c7-4228-8951-a381beafabee"/>
-    <ds:schemaRef ds:uri="4d8e724f-ed6c-4b7c-86a4-236d8fc22848"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>